--- a/OUTPUT/direct_A4FQD5_Saccharopolyspora_erythraea_NRRL_2338.xlsx
+++ b/OUTPUT/direct_A4FQD5_Saccharopolyspora_erythraea_NRRL_2338.xlsx
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.0014</v>
+        <v>0.001599360255897641</v>
       </c>
     </row>
     <row r="3">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.2338</v>
+        <v>0.23390643742503</v>
       </c>
     </row>
   </sheetData>
